--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487135_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487135_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.5191</v>
+        <v>4.0191</v>
       </c>
       <c r="E2" t="n">
-        <v>9.429500000000001</v>
+        <v>6.3846</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.9104</v>
+        <v>-2.3655</v>
       </c>
       <c r="G2" t="n">
         <v>-0.4429</v>
@@ -610,13 +610,13 @@
         <v>1.5441</v>
       </c>
       <c r="S2" t="n">
-        <v>5.4988</v>
+        <v>1.9988</v>
       </c>
       <c r="T2" t="n">
-        <v>5.0262</v>
+        <v>1.9814</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4726</v>
+        <v>0.0175</v>
       </c>
       <c r="V2" t="n">
         <v>1.8842</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. MUZQUIZ GURREA</t>
+          <t>R. SANCHEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.3544</v>
+        <v>-0.9098000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8721</v>
+        <v>2.7768</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.2265</v>
+        <v>-3.6867</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.7068</v>
+        <v>-0.5339</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2318</v>
+        <v>2.3836</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.9386</v>
+        <v>-2.9175</v>
       </c>
       <c r="J3" t="n">
-        <v>1.2087</v>
+        <v>3.2626</v>
       </c>
       <c r="K3" t="n">
-        <v>1.0866</v>
+        <v>3.3119</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1221</v>
+        <v>-0.0492</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.9155</v>
+        <v>-3.7965</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.8548</v>
+        <v>-0.9283</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.0607</v>
+        <v>-2.8682</v>
       </c>
       <c r="P3" t="n">
-        <v>0.772</v>
+        <v>0.965</v>
       </c>
       <c r="Q3" t="n">
         <v>-0.965</v>
       </c>
       <c r="R3" t="n">
-        <v>1.7371</v>
+        <v>1.9301</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5804</v>
+        <v>-0.113</v>
       </c>
       <c r="T3" t="n">
-        <v>2.3426</v>
+        <v>0.4793</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.7622</v>
+        <v>-0.5923</v>
       </c>
       <c r="V3" t="n">
+        <v>-1.228</v>
+      </c>
+      <c r="W3" t="n">
         <v>0</v>
       </c>
-      <c r="W3" t="n">
-        <v>0.2859</v>
-      </c>
       <c r="X3" t="n">
-        <v>-0.2859</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. SANCHEZ SANCHEZ</t>
+          <t>D. MUZQUIZ GURREA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-2.4784</v>
+        <v>-1.1357</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3154</v>
+        <v>1.9302</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.7937</v>
+        <v>-3.0659</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.5339</v>
+        <v>-1.7068</v>
       </c>
       <c r="H4" t="n">
-        <v>2.3836</v>
+        <v>0.2318</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.9175</v>
+        <v>-1.9386</v>
       </c>
       <c r="J4" t="n">
-        <v>3.2626</v>
+        <v>1.2087</v>
       </c>
       <c r="K4" t="n">
-        <v>3.3119</v>
+        <v>1.0866</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.0492</v>
+        <v>0.1221</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.7965</v>
+        <v>-2.9155</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.9283</v>
+        <v>-0.8548</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.8682</v>
+        <v>-2.0607</v>
       </c>
       <c r="P4" t="n">
-        <v>0.965</v>
+        <v>0.772</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.965</v>
       </c>
       <c r="R4" t="n">
-        <v>1.9301</v>
+        <v>1.7371</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.6815</v>
+        <v>-0.2009</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9822</v>
+        <v>1.4007</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6993</v>
+        <v>-1.6016</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.228</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.228</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-3.5969</v>
+        <v>-2.1146</v>
       </c>
       <c r="E5" t="n">
-        <v>0.08450000000000001</v>
+        <v>1.2455</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.6814</v>
+        <v>-3.3601</v>
       </c>
       <c r="G5" t="n">
         <v>-3.5788</v>
@@ -844,13 +844,13 @@
         <v>1.5441</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.8058</v>
+        <v>-0.3235</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6107</v>
+        <v>0.5503</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.1951</v>
+        <v>-0.8739</v>
       </c>
       <c r="V5" t="n">
         <v>0.2436</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-3.8655</v>
+        <v>-3.3856</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2367</v>
+        <v>0.3235</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.6288</v>
+        <v>-3.7091</v>
       </c>
       <c r="G6" t="n">
         <v>0.1372</v>
@@ -922,13 +922,13 @@
         <v>1.9301</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.1957</v>
+        <v>-0.7159</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4614</v>
+        <v>0.0988</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7344000000000001</v>
+        <v>-0.8147</v>
       </c>
       <c r="V6" t="n">
         <v>-1.842</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.9275</v>
+        <v>-3.4477</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.8253</v>
+        <v>-2.2651</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.1023</v>
+        <v>-1.1826</v>
       </c>
       <c r="G7" t="n">
         <v>-7.7739</v>
@@ -1000,13 +1000,13 @@
         <v>2.1231</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0535</v>
+        <v>0.4263</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7099</v>
+        <v>1.2701</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7635</v>
+        <v>-0.8438</v>
       </c>
       <c r="V7" t="n">
         <v>2.7418</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.3286</v>
+        <v>-4.3564</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.137</v>
+        <v>-0.9774</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.1916</v>
+        <v>-3.379</v>
       </c>
       <c r="G8" t="n">
         <v>-6.8377</v>
@@ -1078,13 +1078,13 @@
         <v>2.1231</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7793</v>
+        <v>0.7516</v>
       </c>
       <c r="T8" t="n">
-        <v>0.9162</v>
+        <v>1.0758</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1369</v>
+        <v>-0.3242</v>
       </c>
       <c r="V8" t="n">
         <v>0.5717</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. DE CASTRO AYALA</t>
+          <t>J. LAMBAS VIVANCOS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.6158</v>
+        <v>-4.3873</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5893</v>
+        <v>-0.9479</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.0265</v>
+        <v>-3.4394</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.9103</v>
+        <v>-3.9469</v>
       </c>
       <c r="H9" t="n">
-        <v>0.326</v>
+        <v>-1.8434</v>
       </c>
       <c r="I9" t="n">
-        <v>-4.2363</v>
+        <v>-2.1035</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.2747</v>
+        <v>-1.545</v>
       </c>
       <c r="K9" t="n">
-        <v>1.3143</v>
+        <v>-0.8282</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.589</v>
+        <v>-0.7169</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.6356</v>
+        <v>-2.4018</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9883</v>
+        <v>-1.0152</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.6473</v>
+        <v>-1.3866</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.386</v>
+        <v>-0</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.9301</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5441</v>
+        <v>1.9301</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5804</v>
+        <v>0.1735</v>
       </c>
       <c r="T9" t="n">
-        <v>1.6155</v>
+        <v>1.2992</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.0351</v>
+        <v>-1.1257</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.8999</v>
+        <v>-0.614</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.228</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.8999</v>
+        <v>-1.842</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. LAMBAS VIVANCOS</t>
+          <t>A. DE CASTRO AYALA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.8617</v>
+        <v>-5.1968</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.3687</v>
+        <v>-2.331</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.4929</v>
+        <v>-2.8659</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.9469</v>
+        <v>-3.9103</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.8434</v>
+        <v>0.326</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.1035</v>
+        <v>-4.2363</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.545</v>
+        <v>-1.2747</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.8282</v>
+        <v>1.3143</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7169</v>
+        <v>-2.589</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.4018</v>
+        <v>-2.6356</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.0152</v>
+        <v>-0.9883</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.3866</v>
+        <v>-1.6473</v>
       </c>
       <c r="P10" t="n">
-        <v>-0</v>
+        <v>-0.386</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.9301</v>
       </c>
       <c r="R10" t="n">
-        <v>1.9301</v>
+        <v>1.5441</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3008</v>
+        <v>-0.0007</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1216</v>
+        <v>0.8739</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.1792</v>
+        <v>-0.8745000000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.614</v>
+        <v>-0.8999</v>
       </c>
       <c r="W10" t="n">
-        <v>1.228</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.842</v>
+        <v>-0.8999</v>
       </c>
     </row>
     <row r="11">
@@ -1267,25 +1267,25 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-21.5097</v>
+        <v>-20.9148</v>
       </c>
       <c r="E11" t="n">
-        <v>5.544500000000001</v>
+        <v>6.139200000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-27.0541</v>
+        <v>-27.0542</v>
       </c>
       <c r="G11" t="n">
         <v>-28.594</v>
       </c>
       <c r="H11" t="n">
-        <v>-5.574</v>
+        <v>-5.573999999999999</v>
       </c>
       <c r="I11" t="n">
         <v>-23.0201</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2636000000000003</v>
+        <v>0.2635999999999996</v>
       </c>
       <c r="K11" t="n">
         <v>4.0761</v>
@@ -1297,7 +1297,7 @@
         <v>-28.8574</v>
       </c>
       <c r="N11" t="n">
-        <v>-9.650099999999998</v>
+        <v>-9.6501</v>
       </c>
       <c r="O11" t="n">
         <v>-19.2072</v>
@@ -1312,13 +1312,13 @@
         <v>16.4059</v>
       </c>
       <c r="S11" t="n">
-        <v>1.4016</v>
+        <v>1.9962</v>
       </c>
       <c r="T11" t="n">
-        <v>8.4345</v>
+        <v>9.029500000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>-7.0331</v>
+        <v>-7.0332</v>
       </c>
       <c r="V11" t="n">
         <v>0.8574000000000001</v>
@@ -1327,7 +1327,7 @@
         <v>8.4268</v>
       </c>
       <c r="X11" t="n">
-        <v>-7.5693</v>
+        <v>-7.569299999999999</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>9.350300000000001</v>
+        <v>11.1396</v>
       </c>
       <c r="E12" t="n">
-        <v>8.604699999999999</v>
+        <v>9.8064</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7456</v>
+        <v>1.3332</v>
       </c>
       <c r="G12" t="n">
         <v>10.1471</v>
@@ -1390,13 +1390,13 @@
         <v>1.9301</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.4853</v>
+        <v>-0.696</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6993</v>
+        <v>0.5024</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.786</v>
+        <v>-1.1984</v>
       </c>
       <c r="V12" t="n">
         <v>4.5838</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.0821</v>
+        <v>6.9076</v>
       </c>
       <c r="E13" t="n">
-        <v>4.9985</v>
+        <v>4.7982</v>
       </c>
       <c r="F13" t="n">
-        <v>2.0837</v>
+        <v>2.1094</v>
       </c>
       <c r="G13" t="n">
         <v>4.7106</v>
@@ -1468,13 +1468,13 @@
         <v>1.3511</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1242</v>
+        <v>-0.0503</v>
       </c>
       <c r="T13" t="n">
-        <v>1.244</v>
+        <v>1.0437</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.1198</v>
+        <v>-1.094</v>
       </c>
       <c r="V13" t="n">
         <v>2.8263</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.6314</v>
+        <v>5.653</v>
       </c>
       <c r="E14" t="n">
-        <v>3.6663</v>
+        <v>4.3673</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9651999999999999</v>
+        <v>1.2857</v>
       </c>
       <c r="G14" t="n">
         <v>5.9539</v>
@@ -1546,13 +1546,13 @@
         <v>2.1231</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5275</v>
+        <v>0.4941</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2512</v>
+        <v>0.9522</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7786999999999999</v>
+        <v>-0.4581</v>
       </c>
       <c r="V14" t="n">
         <v>0.9421</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. TOURE</t>
+          <t>A. RUIZ FERNÁNDEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8329</v>
+        <v>1.7318</v>
       </c>
       <c r="E15" t="n">
-        <v>3.6214</v>
+        <v>1.9589</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.7886</v>
+        <v>-0.2271</v>
       </c>
       <c r="G15" t="n">
-        <v>1.4197</v>
+        <v>0.8098</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2309</v>
+        <v>-0.2598</v>
       </c>
       <c r="I15" t="n">
-        <v>1.1888</v>
+        <v>1.0696</v>
       </c>
       <c r="J15" t="n">
-        <v>1.2659</v>
+        <v>1.3638</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8589</v>
+        <v>0.0207</v>
       </c>
       <c r="L15" t="n">
-        <v>0.407</v>
+        <v>1.3431</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1538</v>
+        <v>-0.5538999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.628</v>
+        <v>-0.2805</v>
       </c>
       <c r="O15" t="n">
-        <v>0.7818000000000001</v>
+        <v>-0.2735</v>
       </c>
       <c r="P15" t="n">
-        <v>1.7371</v>
+        <v>0.193</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7371</v>
+        <v>0.193</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4601</v>
+        <v>0.115</v>
       </c>
       <c r="T15" t="n">
-        <v>2.6837</v>
+        <v>-0.0188</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.2235</v>
+        <v>0.1338</v>
       </c>
       <c r="V15" t="n">
-        <v>-2.784</v>
+        <v>0.614</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.3281</v>
+        <v>0.614</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.4559</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.7267</v>
+        <v>1.1999</v>
       </c>
       <c r="E16" t="n">
-        <v>3.1923</v>
+        <v>2.291</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.4655</v>
+        <v>-1.0911</v>
       </c>
       <c r="G16" t="n">
         <v>1.6331</v>
@@ -1702,13 +1702,13 @@
         <v>0.579</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4567</v>
+        <v>-0.0701</v>
       </c>
       <c r="T16" t="n">
-        <v>1.4674</v>
+        <v>0.5662</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.0107</v>
+        <v>-0.6362</v>
       </c>
       <c r="V16" t="n">
         <v>-0.9421</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. RUIZ FERNÁNDEZ</t>
+          <t>A. TOURE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5514</v>
+        <v>1.0522</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8588</v>
+        <v>2.1193</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3074</v>
+        <v>-1.0671</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8098</v>
+        <v>1.4197</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2598</v>
+        <v>0.2309</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0696</v>
+        <v>1.1888</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3638</v>
+        <v>1.2659</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0207</v>
+        <v>0.8589</v>
       </c>
       <c r="L17" t="n">
-        <v>1.3431</v>
+        <v>0.407</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5538999999999999</v>
+        <v>0.1538</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2805</v>
+        <v>-0.628</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2735</v>
+        <v>0.7818000000000001</v>
       </c>
       <c r="P17" t="n">
-        <v>0.193</v>
+        <v>1.7371</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.193</v>
+        <v>1.7371</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0654</v>
+        <v>0.6795</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.119</v>
+        <v>1.1815</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0535</v>
+        <v>-0.5021</v>
       </c>
       <c r="V17" t="n">
-        <v>0.614</v>
+        <v>-2.784</v>
       </c>
       <c r="W17" t="n">
-        <v>0.614</v>
+        <v>-0.3281</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-2.4559</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0508</v>
+        <v>0.4186</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0543</v>
+        <v>0.7538</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.0035</v>
+        <v>-0.3352</v>
       </c>
       <c r="G18" t="n">
         <v>1.3266</v>
@@ -1858,13 +1858,13 @@
         <v>1.7371</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5341</v>
+        <v>-0.1662</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9333</v>
+        <v>0.6329</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.4674</v>
+        <v>-0.7992</v>
       </c>
       <c r="V18" t="n">
         <v>-1.5138</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. HERNÁNDEZ MARTÍN</t>
+          <t>M. CARRETERO GARCÍA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0446</v>
+        <v>0.2471</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1283</v>
+        <v>1.3997</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1729</v>
+        <v>-1.1526</v>
       </c>
       <c r="G19" t="n">
-        <v>1.3116</v>
+        <v>2.0747</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6997</v>
+        <v>-0.2566</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6119</v>
+        <v>2.3313</v>
       </c>
       <c r="J19" t="n">
-        <v>1.6119</v>
+        <v>2.0613</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9936</v>
+        <v>0.1242</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6183999999999999</v>
+        <v>1.9371</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.3003</v>
+        <v>0.0134</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2939</v>
+        <v>-0.3808</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0064</v>
+        <v>0.3941</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.772</v>
+        <v>-0.965</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.965</v>
       </c>
       <c r="R19" t="n">
-        <v>0.193</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1613</v>
+        <v>0.0373</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.119</v>
+        <v>0.3034</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2802</v>
+        <v>-0.2661</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.6562</v>
+        <v>-0.8999</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.6562</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.8999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. VASQUEZ BAUTISTA</t>
+          <t>C. HERNÁNDEZ MARTÍN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.633</v>
+        <v>0.1844</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1584</v>
+        <v>0.1721</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4746</v>
+        <v>0.0123</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.6941000000000001</v>
+        <v>1.3116</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.0297</v>
+        <v>0.6997</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3356</v>
+        <v>0.6119</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6004</v>
+        <v>1.6119</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.295</v>
+        <v>0.9936</v>
       </c>
       <c r="L20" t="n">
-        <v>0.8954</v>
+        <v>0.6183999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.2945</v>
+        <v>-0.3003</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7347</v>
+        <v>-0.2939</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5598</v>
+        <v>-0.0064</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.579</v>
+        <v>-0.772</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.965</v>
       </c>
       <c r="R20" t="n">
-        <v>0.386</v>
+        <v>0.193</v>
       </c>
       <c r="S20" t="n">
-        <v>0.926</v>
+        <v>0.3011</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2062</v>
+        <v>0.1814</v>
       </c>
       <c r="U20" t="n">
-        <v>0.7198</v>
+        <v>0.1196</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.2859</v>
+        <v>-0.6562</v>
       </c>
       <c r="W20" t="n">
+        <v>-0.6562</v>
+      </c>
+      <c r="X20" t="n">
         <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>-0.2859</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. CARRETERO GARCÍA</t>
+          <t>A. VASQUEZ BAUTISTA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.7281</v>
+        <v>-0.8753</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7989000000000001</v>
+        <v>0.2421</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.527</v>
+        <v>-1.1174</v>
       </c>
       <c r="G21" t="n">
-        <v>2.0747</v>
+        <v>-0.6941000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2566</v>
+        <v>-1.0297</v>
       </c>
       <c r="I21" t="n">
-        <v>2.3313</v>
+        <v>0.3356</v>
       </c>
       <c r="J21" t="n">
-        <v>2.0613</v>
+        <v>0.6004</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1242</v>
+        <v>-0.295</v>
       </c>
       <c r="L21" t="n">
-        <v>1.9371</v>
+        <v>0.8954</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0134</v>
+        <v>-1.2945</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3808</v>
+        <v>-0.7347</v>
       </c>
       <c r="O21" t="n">
-        <v>0.3941</v>
+        <v>-0.5598</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.965</v>
+        <v>-0.579</v>
       </c>
       <c r="Q21" t="n">
         <v>-0.965</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>0.386</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9379</v>
+        <v>0.6838</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2974</v>
+        <v>0.6068</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6405</v>
+        <v>0.077</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.8999</v>
+        <v>-0.2859</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.8999</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.3993</v>
+        <v>-3.479</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.4543</v>
+        <v>-0.8548</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.945</v>
+        <v>-2.6241</v>
       </c>
       <c r="G22" t="n">
         <v>-0.099</v>
@@ -2170,13 +2170,13 @@
         <v>1.3511</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0205</v>
+        <v>-0.0592</v>
       </c>
       <c r="T22" t="n">
-        <v>1.482</v>
+        <v>1.0814</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.4615</v>
+        <v>-1.1406</v>
       </c>
       <c r="V22" t="n">
         <v>-2.7418</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>21.5098</v>
+        <v>24.1799</v>
       </c>
       <c r="E23" t="n">
-        <v>27.0542</v>
+        <v>27.054</v>
       </c>
       <c r="F23" t="n">
-        <v>-5.5442</v>
+        <v>-2.874</v>
       </c>
       <c r="G23" t="n">
         <v>28.594</v>
@@ -2221,16 +2221,16 @@
         <v>23.0201</v>
       </c>
       <c r="J23" t="n">
-        <v>28.85750000000001</v>
+        <v>28.8575</v>
       </c>
       <c r="K23" t="n">
-        <v>9.6502</v>
+        <v>9.650200000000002</v>
       </c>
       <c r="L23" t="n">
         <v>19.2074</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.2633</v>
+        <v>-0.2632999999999999</v>
       </c>
       <c r="N23" t="n">
         <v>-4.0762</v>
@@ -2239,7 +2239,7 @@
         <v>3.8127</v>
       </c>
       <c r="P23" t="n">
-        <v>-4.825099999999999</v>
+        <v>-4.8251</v>
       </c>
       <c r="Q23" t="n">
         <v>-16.4056</v>
@@ -2248,19 +2248,19 @@
         <v>11.5806</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.4014</v>
+        <v>1.269</v>
       </c>
       <c r="T23" t="n">
-        <v>7.0331</v>
+        <v>7.033099999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>-8.4346</v>
+        <v>-5.7643</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.8574999999999999</v>
+        <v>-0.8574999999999988</v>
       </c>
       <c r="W23" t="n">
-        <v>7.5694</v>
+        <v>7.569400000000002</v>
       </c>
       <c r="X23" t="n">
         <v>-8.4269</v>
